--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1707-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1707-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EB65301-4F4A-4644-97DA-455011B152AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AC8A4A2-3504-461B-9C16-5246F306783F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{31224FA5-2D7F-439D-85FF-F93502C52FFA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{988F2CC5-9AC1-45CE-A8A1-E2B072AFAA4D}"/>
   </bookViews>
   <sheets>
     <sheet name="1707-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1576,28 +1576,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A2B26C-92A0-4164-ACB0-077D3C210AA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ADD8A4A-77F3-4514-9622-46F634ECA06D}">
   <dimension ref="A1:X50"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1631,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1787,7 +1787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1895,7 +1895,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2024</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2023</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>2022</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>2021</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>2020</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>2019</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>2018</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2017</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="47">
         <v>2016</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>2015</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2014</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="49">
         <v>2013</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>2012</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>2011</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="47">
         <v>2010</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="49">
         <v>2009</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="47">
         <v>2008</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="49">
         <v>2007</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="47">
         <v>2006</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="49">
         <v>2005</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>2004</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="49">
         <v>2003</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="47">
         <v>2002</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="49">
         <v>2001</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="47">
         <v>2000</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="49">
         <v>1999</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>1998</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="49">
         <v>1997</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="47">
         <v>1996</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="49">
         <v>1995</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="47">
         <v>1994</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="49">
         <v>1993</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="47">
         <v>1992</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="49">
         <v>1991</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="47">
         <v>1990</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="49">
         <v>1989</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="47">
         <v>1988</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="49">
         <v>1987</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="47">
         <v>1984</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="49">
         <v>1983</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="47" t="s">
         <v>65</v>
       </c>
